--- a/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_17-09-2026.xlsx
+++ b/Compititor's_Price/Powerlon_Prices/Powerlon_Prices_17-09-2026.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267dedc3cd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>£28.60</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df7aa190&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
     </row>
@@ -552,27 +552,57 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£42.73</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultraperm-standard-underlay-115gsm-all-sizes?variant=42235579007169 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-ultraperm-standard-breather-membrane-roof-felt-1m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-ultraperm-standard-breather-membrane-roof-felt-1m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.roofingoutlet.co.uk/products/powerlon-ultraperm-standard-breather-membrane-roof-felt-1m-x-50m</t>
+          <t>Error: HTTPSConnectionPool(host='www.roofingoutlet.co.uk', port=443): Max retries exceeded with url: /products/powerlon-ultraperm-standard-breather-membrane-roof-felt-1m-x-50m (Caused by NameResolutionError("HTTPSConnection(host='www.roofingoutlet.co.uk', port=443): Failed to resolve 'www.roofingoutlet.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df6b32d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -589,17 +619,47 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£64.08</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultraperm-standard-underlay-115gsm-all-sizes?variant=42235579236545 (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='build4less.co.uk', port=443) at 0x22b42a3c910&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-ultraperm-standard-breather-membrane-roof-felt-15m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-ultraperm-standard-breather-membrane-roof-felt-15m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -609,7 +669,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df59a050&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_standard_115gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -626,17 +686,47 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£57.53</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultraperm-premium-underlay-135gsm-all-sizes (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-ultraperm-premium-breather-membrane-roof-felt-1m-x-50m-roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-ultraperm-premium-breather-membrane-roof-felt-1m-x-50m-roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,7 +736,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df7da650&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -663,17 +753,47 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£86.37</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultraperm-premium-underlay-135gsm-all-sizes?variant=42235747926209 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-ultraperm-premium-breather-membrane-roof-felt-15m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-ultraperm-premium-breather-membrane-roof-felt-15m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -683,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267e01b7850&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_premium_135gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -700,17 +820,47 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£112.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultraperm-max-underlay-155gsm-all-sizes (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-ultraperm-max-breather-membrane-roof-felt-1m-x-50m-roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-ultraperm-max-breather-membrane-roof-felt-1m-x-50m-roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£156.85ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -720,7 +870,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267dee60f90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.0m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -737,17 +887,47 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£112.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultraperm-max-underlay-155gsm-all-sizes?variant=42236051620033 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-ultraperm-max-breather-membrane-roof-felt-15m-x-50m-roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-ultraperm-max-breather-membrane-roof-felt-15m-x-50m-roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -757,7 +937,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267e0a315d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_max_155gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -774,7 +954,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£10.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/acrylic-jointing-tape-60mm-x-25m (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -784,7 +964,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -811,17 +1021,47 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£103.77</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/supaperm-sp100-housewrap-breather-membrane-all-sizes (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-supaperm-100-house-wrap-breather-membrane-16m-x-100m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-supaperm-100-house-wrap-breather-membrane-16m-x-100m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -831,7 +1071,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_1.6m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267dfec7390&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_1.6m_x_100m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -848,41 +1088,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£199.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/supaperm-sp100-housewrap-breather-membrane-all-sizes?variant=42236484616385 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-supaperm-100-house-wrap-breather-membrane-27m-x-100m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-supaperm-100-house-wrap-breather-membrane-27m-x-100m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: invalid argument
-  (Session info: chrome=153.0.8010.37)
+  (Session info: chrome=153.0.8010.48)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff679e8ff25+5ae5]
-	chromedriver!(No symbol) [0x7ff679db2210]
-	chromedriver!(No symbol) [0x7ff679bd4896]
-	chromedriver!(No symbol) [0x7ff679bc113d]
-	chromedriver!(No symbol) [0x7ff679bbf694]
-	chromedriver!(No symbol) [0x7ff679bbfc12]
-	chromedriver!(No symbol) [0x7ff679bd8d87]
-	chromedriver!(No symbol) [0x7ff679c80ea4]
-	chromedriver!(No symbol) [0x7ff679c598fa]
-	chromedriver!(No symbol) [0x7ff679c800df]
-	chromedriver!(No symbol) [0x7ff679c22202]
-	chromedriver!(No symbol) [0x7ff679c23013]
-	chromedriver!GetHandleVerifier [0x7ff67a2b4231+429df1]
-	chromedriver!GetHandleVerifier [0x7ff67a2dfce7+4558a7]
-	chromedriver!GetHandleVerifier [0x7ff67a2d413e+449cfe]
-	chromedriver!GetHandleVerifier [0x7ff679f8c9ce+10258e]
-	chromedriver!(No symbol) [0x7ff679dc0545]
-	chromedriver!(No symbol) [0x7ff679dbb6a4]
-	chromedriver!(No symbol) [0x7ff679dbb834]
-	chromedriver!(No symbol) [0x7ff679da601c]
-	KERNEL32!BaseThreadInitThunk [0x7ffc7495cd87+17]
-	ntdll!RtlUserThreadStart [0x7ffc7544caec+2c]
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4876]
+	chromedriver!(No symbol) [0x7ff6160b111d]
+	chromedriver!(No symbol) [0x7ff6160af674]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
 </t>
         </is>
       </c>
@@ -893,7 +1133,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_2.7m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267dece1d90&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_2.7m_x_100m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -910,17 +1150,47 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£147.70</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/vcl-250-air-and-vapour-control-layer-2m-x-50m-100m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-vcl-250-air-and-vapour-control-layer-2m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-vcl-250-air-and-vapour-control-layer-2m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -930,7 +1200,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_250_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df457290&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_250_vapour_control_layer_2m_x_50mm_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -947,17 +1217,47 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£81.81</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultrablock-200-thermo-reflective-vapour-control-layer-1-6m-x-50m-80m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-ultrablock-al-200-vapour-control-layer-16m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-ultrablock-al-200-vapour-control-layer-16m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -967,7 +1267,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_200_thermo_reflective_vapour_control_layer_1.6m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df7ed250&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_200_thermo_reflective_vapour_control_layer_1.6m_x_50mm_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -984,17 +1284,47 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/air-barrier-membrane-1-5m-x-50m-75m2</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/air-barrier-membrane-1-5m-x-50m-75m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-air-barrier-membrane-15m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-air-barrier-membrane-15m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£156.85ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1004,7 +1334,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_air_barrier_membrane_1.5m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df5cf790&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_air_barrier_membrane_1.5m_x_50mm_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1351,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£260.40</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-multigas-300-gas-barrier-membrane-50m-x-2m-100m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-powerbase-gas-barrier-membrane-multigas-300-50m-x-2m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-powerbase-gas-barrier-membrane-multigas-300-50m-x-2m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1095,17 +1425,47 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>£148.52</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/flameout-timber-frame-house-wrap-breather-membrane-1-5m-x-50m-75m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-flameout-house-wrap-breather-membrane-15m-x-50m-roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-flameout-house-wrap-breather-membrane-15m-x-50m-roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1132,17 +1492,47 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£119.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/vcl-170-air-and-vapour-control-layer-2m-x-50m-100m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-vcl-170-air-and-vapour-control-layer-2m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-vcl-170-air-and-vapour-control-layer-2m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1152,7 +1542,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_170_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267ded4d710&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_vcl_170_vapour_control_layer_2m_x_50mm_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1559,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£208.60</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/reinforced-protective-membrane-4m-x-50m-200m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1179,7 +1569,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_INTERNET_DISCONNECTED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1206,17 +1626,47 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£267.12</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/uv-160-sa-facade-membrane-1-5m-x-50m-75m2 (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='build4less.co.uk', port=443) at 0x22b42a3da10&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-uv-160-sa-breathable-facade-membrane-15m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-uv-160-sa-breathable-facade-membrane-15m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1226,7 +1676,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv160sa_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267dfdd8e10&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv160sa_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/powerlon-uv-145-powerlon-uv-145-fr-class-b-uv-stable-breather-membrane-2-5m-x-40m-100-m2</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerlon-uv-145-powerlon-uv-145-fr-class-b-uv-stable-breather-membrane-2-5m-x-40m-100-m2 (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='build4less.co.uk', port=443) at 0x22b41200d10&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1280,17 +1730,47 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£209.69</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/uv-120-black-facade-membrane-1-5m-x-50m-75m2 (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='build4less.co.uk', port=443) at 0x22b42a4d910&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-uv-120-breathable-facade-membrane-15m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-uv-120-breathable-facade-membrane-15m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1300,7 +1780,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv120_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267e08a1990&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv120_uv_resistant_facade_membrane_1.5m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1317,17 +1797,47 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>£24.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerlon-uv-facade-tape-60mm-x-25m (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='build4less.co.uk', port=443) at 0x22b42a4d7d0&gt;, 'Connection to build4less.co.uk timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-uv-facade-tape-60mm-x-25m-roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-uv-facade-tape-60mm-x-25m-roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1337,7 +1847,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv_facade_tape_60mm_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267deeb0810&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_uv_facade_tape_60mm_x_25m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1354,17 +1864,47 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/uv-flex-tape-50mm-x-10m</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/uv-flex-tape-50mm-x-10m (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-uv-flex-tape-75mm-x-10m-roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-uv-flex-tape-75mm-x-10m-roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>£8.69ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1391,17 +1931,47 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£10.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbond-fr-aluminium-vcl-tape-50mm-x-47-5m (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerbond-aluminium-fr-vcl-tape-50mm-x-475m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerbond-aluminium-fr-vcl-tape-50mm-x-475m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1411,7 +1981,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_aluminium_fr_vcl_tape_50mm_x_47.5m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df3988d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_aluminium_fr_vcl_tape_50mm_x_47.5m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1428,17 +1998,47 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£9.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbond-double-sided-butyl-tape-all-sizes (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerbond-double-sided-butyl-tape-2mm-x-15mm-x-24m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerbond-double-sided-butyl-tape-2mm-x-15mm-x-24m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1448,7 +2048,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_double_sided_butyl_tape_2mm_x_15mm_x_24m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267ded76810&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerbond_double_sided_butyl_tape_2mm_x_15mm_x_24m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1465,7 +2065,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>£15.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbond-double-sided-butyl-tape-all-sizes?variant=42253717012673 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1502,7 +2102,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>£8.63</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbond-double-sided-butyl-tape-all-sizes?variant=42253717045441 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1512,7 +2112,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1539,17 +2169,47 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>£8.60</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbond-facade-sealant-for-uv-x-290ml-tube (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-uv-facade-sealant-290ml-tube.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-uv-facade-sealant-290ml-tube.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1576,17 +2236,47 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>£52.45</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultrperm-lite-underlay-92gsm-1-5m-x-50m-75m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-ultraperm-lite-vapour-permeable-underlay-roofing-felt-50m-x-15m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-ultraperm-lite-vapour-permeable-underlay-roofing-felt-50m-x-15m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>£35.01ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1596,7 +2286,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267dedb4350&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultraperm_lite_92gsm_breather_membrane_1.5m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1613,7 +2303,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>£26.90</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/dry-fix-ridge-kit-6m (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1623,7 +2313,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1650,12 +2370,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>£248.50</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/metalix-separation-breather-membrane-1-5m-x-25m-37-5m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-metalix-separation-layer-25m-x-1-5m-roll.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-metalix-separation-layer-25m-x-1-5m-roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1670,7 +2390,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_metalix_metal_roof_separation_layer_1.5m_x_25m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df4d6c50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_metalix_metal_roof_separation_layer_1.5m_x_25m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1687,7 +2407,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>£190.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/supaperm-sp100-housewrap-breather-membrane-3-2m-x-100m-320m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1707,7 +2427,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_3.2m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267dec9e350&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_supaperm_sp100_housewrap_3.2m_x_100m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1724,7 +2444,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/thermaperm-house-wrap-breather-membrane-all-sizes</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/thermaperm-house-wrap-breather-membrane-all-sizes (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1744,7 +2464,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_1.5m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df4d7c50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_1.5m_x_100m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1761,7 +2481,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/thermaperm-house-wrap-breather-membrane-all-sizes?variant=42253555630273</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/thermaperm-house-wrap-breather-membrane-all-sizes?variant=42253555630273 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1781,7 +2501,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_2.7m_x_100m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267dec9e190&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_thermaperm_housewrap_2.7m_x_100m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1798,41 +2518,41 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>£249.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultrablock-300-thermo-reflective-vapour-control-layer-2m-x-50m-100m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/powerlon-ultrablock-300-thermo-reflective-vapour-control-layer-1-6m-x-50m.html</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/powerlon-ultrablock-300-thermo-reflective-vapour-control-layer-1-6m-x-50m.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationsuperstore.co.uk', port=443): Failed to resolve 'www.insulationsuperstore.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: invalid argument
-  (Session info: chrome=153.0.8010.37)
+  (Session info: chrome=153.0.8010.48)
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff679e8ff25+5ae5]
-	chromedriver!(No symbol) [0x7ff679db2210]
-	chromedriver!(No symbol) [0x7ff679bd4896]
-	chromedriver!(No symbol) [0x7ff679bc113d]
-	chromedriver!(No symbol) [0x7ff679bbf694]
-	chromedriver!(No symbol) [0x7ff679bbfc12]
-	chromedriver!(No symbol) [0x7ff679bd8d87]
-	chromedriver!(No symbol) [0x7ff679c80ea4]
-	chromedriver!(No symbol) [0x7ff679c598fa]
-	chromedriver!(No symbol) [0x7ff679c800df]
-	chromedriver!(No symbol) [0x7ff679c22202]
-	chromedriver!(No symbol) [0x7ff679c23013]
-	chromedriver!GetHandleVerifier [0x7ff67a2b4231+429df1]
-	chromedriver!GetHandleVerifier [0x7ff67a2dfce7+4558a7]
-	chromedriver!GetHandleVerifier [0x7ff67a2d413e+449cfe]
-	chromedriver!GetHandleVerifier [0x7ff679f8c9ce+10258e]
-	chromedriver!(No symbol) [0x7ff679dc0545]
-	chromedriver!(No symbol) [0x7ff679dbb6a4]
-	chromedriver!(No symbol) [0x7ff679dbb834]
-	chromedriver!(No symbol) [0x7ff679da601c]
-	KERNEL32!BaseThreadInitThunk [0x7ffc7495cd87+17]
-	ntdll!RtlUserThreadStart [0x7ffc7544caec+2c]
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4876]
+	chromedriver!(No symbol) [0x7ff6160b111d]
+	chromedriver!(No symbol) [0x7ff6160af674]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
 </t>
         </is>
       </c>
@@ -1843,7 +2563,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_300_thermo_reflective_vapour_control_layer_2m_x_50mm_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267e00284d0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_ultrablock_300_thermo_reflective_vapour_control_layer_2m_x_50mm_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -1860,7 +2580,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>£507.93</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/ultrablock-self-adhesive-thermo-refelective-vapour-control-layer-1-5m-x-100m-150m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1870,7 +2590,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1897,7 +2647,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>£208.60</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/reinforced-protective-membrane-4m-x-50m-200m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1934,7 +2684,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>£64.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerlon-uv-primer-1000ml (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1944,7 +2694,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1971,7 +2751,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>£148.52</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/flameout-fire-retardant-breather-membrane-all-sizes (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1991,7 +2771,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267dee9fc50&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2788,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>£284.10</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/flameout-fire-retardant-breather-membrane-all-sizes?variant=42253591314625 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2018,7 +2798,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2028,7 +2838,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_3m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df071590&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_breathe_fire_retardant_membrane_3m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2855,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>£13.87</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/flameout-membrane-sealing-tape-60mm-x-25m (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2055,7 +2865,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2082,7 +2922,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>£111.88</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/flameout-block-fire-retardant-vapour-contol-layer-2m-x-50m-100m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2092,7 +2932,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2102,7 +2972,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_fire_retardant_membrane_2m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267df3f0350&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_fire_retardant_membrane_2m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2989,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>£160.67</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/flameout-block-plus-fire-retardant-vapour-contol-layer-2m-x-50m-100m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2129,7 +2999,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2139,7 +3039,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_plus_fire_retardant_membrane_2m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267e0b2d410&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_plus_fire_retardant_membrane_2m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -2156,7 +3056,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>£356.93</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/flameout-block-class-a-fire-retardant-vapour-contol-layer-1-5m-x-50m-75m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2176,7 +3076,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_class_a_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by ConnectTimeoutError(&lt;HTTPSConnection(host='www.insulationshop.co', port=443) at 0x267e0b3ccd0&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=None)'))</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /powerlon_flameout_block_class_a_fire_retardant_membrane_1.5m_x_50m_roll.html (Caused by NameResolutionError("HTTPSConnection(host='www.insulationshop.co', port=443): Failed to resolve 'www.insulationshop.co' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
     </row>
@@ -2193,7 +3093,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>£160.67</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/flameout-block-plus-fire-retardant-vapour-contol-layer-2m-x-50m-100m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2230,7 +3130,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>£874.95</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-voc-hydrocarbon-barrier-membrane-3m-x-50m-150m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2267,7 +3167,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>£326.33</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-multigas-500-gas-barrier-membrane-2m-x-50m-100m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2341,7 +3241,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/powerbase-low-perm-gas-barrier-membrane-500mu-4m-x-12-5m-50m2</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-low-perm-gas-barrier-membrane-500mu-4m-x-12-5m-50m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2378,7 +3278,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/powerbase-radon-barrier-membrane-400mu-4m-x-20m-80m2</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-radon-barrier-membrane-400mu-4m-x-20m-80m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2415,7 +3315,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/powerbase-multigas-300-self-adhesive-gas-barrier-membrane-1-08m-x-30m</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-multigas-300-self-adhesive-gas-barrier-membrane-1-08m-x-30m (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2452,7 +3352,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>£17.48</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbond-foil-tape-75mm-x-50m (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2462,7 +3362,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Was:£0.00ex VAT</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_NAME_NOT_RESOLVED
+  (Session info: chrome=153.0.8010.48)
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff61637c895+5aa5]
+	chromedriver!(No symbol) [0x7ff6162a0570]
+	chromedriver!(No symbol) [0x7ff6160c4a7d]
+	chromedriver!(No symbol) [0x7ff6160c186b]
+	chromedriver!(No symbol) [0x7ff6160b1d91]
+	chromedriver!(No symbol) [0x7ff6160b3bd4]
+	chromedriver!(No symbol) [0x7ff6160b2324]
+	chromedriver!(No symbol) [0x7ff6160b1afb]
+	chromedriver!(No symbol) [0x7ff6160b17b1]
+	chromedriver!(No symbol) [0x7ff6160af480]
+	chromedriver!(No symbol) [0x7ff6160afbf2]
+	chromedriver!(No symbol) [0x7ff6160c8d67]
+	chromedriver!(No symbol) [0x7ff616170e44]
+	chromedriver!(No symbol) [0x7ff6161498aa]
+	chromedriver!(No symbol) [0x7ff61617008f]
+	chromedriver!(No symbol) [0x7ff6161121e2]
+	chromedriver!(No symbol) [0x7ff616112ff3]
+	chromedriver!GetHandleVerifier [0x7ff61679b271+424481]
+	chromedriver!GetHandleVerifier [0x7ff6167c6f77+450187]
+	chromedriver!GetHandleVerifier [0x7ff6167bae6e+44407e]
+	chromedriver!GetHandleVerifier [0x7ff61647798e+100b9e]
+	chromedriver!(No symbol) [0x7ff6162ae2b5]
+	chromedriver!(No symbol) [0x7ff6162a9454]
+	chromedriver!(No symbol) [0x7ff6162a95e4]
+	chromedriver!(No symbol) [0x7ff61629438c]
+	KERNEL32!BaseThreadInitThunk [0x7ffe2f28cd87+17]
+	ntdll!RtlUserThreadStart [0x7ffe3000caec+2c]
+</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2489,7 +3419,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>£162.53</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbond-foil-detailing-tape-1m-x-20m (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2600,7 +3530,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>£12.93</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-multigas-300-corners (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2637,7 +3567,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>£14.89</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-voc-corners (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2674,7 +3604,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>£14.89</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-voc-corners (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2711,7 +3641,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>£15.60</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-voc-top-hats (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2748,7 +3678,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>£16.38</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-voc-top-hats?variant=42253894746305 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2785,7 +3715,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>£16.77</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-voc-top-hats?variant=42253894779073 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2822,7 +3752,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>£16.97</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-voc-top-hats?variant=42253894811841 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2859,7 +3789,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>£17.32</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerbase-voc-top-hats?variant=42253894844609 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2933,7 +3863,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/powerlon-safe-one-fr-a2-breather-membrane-2-65m-x-20m-53m2</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerlon-safe-one-fr-a2-breather-membrane-2-65m-x-20m-53m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3044,7 +3974,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>£64.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-lite-scaffold-sheeting-2m-x-45m-90m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3081,7 +4011,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>£69.90</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-standard-scaffold-sheeting-all-sizes (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3118,7 +4048,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>£69.90</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-standard-scaffold-sheeting-all-sizes?variant=47480197480641 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3155,7 +4085,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>£108.50</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-standard-scaffold-sheeting-all-sizes?variant=47480197513409 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3192,7 +4122,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>£228.70</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-standard-xl-scaffold-sheeting-4m-x-45m-180m2 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3229,7 +4159,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>£20.95</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-scaffold-sheeting-toggle-ties-bag-of-100 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3266,7 +4196,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>£137.50</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-standard-fire-retardant-scaffold-sheeting-all-sizes (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3303,7 +4233,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>£137.50</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-standard-fire-retardant-scaffold-sheeting-all-sizes?variant=47480175460545 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3340,7 +4270,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>£201.50</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-standard-fire-retardant-scaffold-sheeting-all-sizes?variant=47480175493313 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3377,7 +4307,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>£171.77</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-premium-fire-retardant-scaffold-sheeting-all-sizes (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3414,7 +4344,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>£258.30</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-premium-fire-retardant-scaffold-sheeting-all-sizes?variant=47480191287489 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3451,7 +4381,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>£474.60</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-premium-fire-retardant-scaffold-sheeting-all-sizes?variant=47480191320257 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3488,7 +4418,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-debris-netting-2m-x-50m-100m2-all-colours (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3525,7 +4455,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-debris-netting-2m-x-50m-100m2-all-colours?variant=47478870376641 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3562,7 +4492,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-debris-netting-2m-x-50m-100m2-all-colours?variant=47478870376641 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3599,7 +4529,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-debris-netting-2m-x-50m-100m2-all-colours?variant=47478870376641 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3636,7 +4566,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-debris-netting-2m-x-50m-100m2-all-colours?variant=47478878372033 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3673,7 +4603,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>£34.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-debris-netting-2m-x-50m-100m2-all-colours?variant=47478878404801 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3710,7 +4640,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>£54.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-fire-retardant-debris-netting-2m-x-50m-100m2-full-range (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3747,7 +4677,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>£54.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-fire-retardant-debris-netting-2m-x-50m-100m2-full-range?variant=47478884925633 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3784,7 +4714,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>£54.80</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-fire-retardant-debris-netting-2m-x-50m-100m2-full-range?variant=47478884958401 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3821,7 +4751,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>£80.60</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-fire-retardant-debris-netting-2m-x-50m-100m2-full-range?variant=47478884991169 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3858,7 +4788,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>£80.60</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-fire-retardant-debris-netting-2m-x-50m-100m2-full-range?variant=47478885023937 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3895,7 +4825,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>£80.60</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-fire-retardant-debris-netting-2m-x-50m-100m2-full-range?variant=47478885056705 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3932,7 +4862,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>£17.99</t>
+          <t>Error: HTTPSConnectionPool(host='build4less.co.uk', port=443): Max retries exceeded with url: /products/powerclad-12-ratchet-ties-bag-of-100 (Caused by NameResolutionError("HTTPSConnection(host='build4less.co.uk', port=443): Failed to resolve 'build4less.co.uk' ([Errno 11001] getaddrinfo failed)"))</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
